--- a/data/LAI_data_S1.xlsx
+++ b/data/LAI_data_S1.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e1df3a5b4952abf3/Dokumente/Promotion/Planung Promotion/Gesamter Ansatz/Morocco/Downskaling/Italiener/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beppe2hd/PycharmProjects/PureCircle/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C87DA2E-959C-4079-8177-82E57963EF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E5892F-07E6-2549-AD93-F4C255211A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7C517B69-0235-47A6-840A-4957514BDF8E}"/>
+    <workbookView xWindow="12880" yWindow="6980" windowWidth="51900" windowHeight="24360" activeTab="1" xr2:uid="{7C517B69-0235-47A6-840A-4957514BDF8E}"/>
   </bookViews>
   <sheets>
     <sheet name="LAI_S1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>DATE</t>
   </si>
@@ -61,12 +59,33 @@
   <si>
     <t>LAI   6 Farmer ICBA</t>
   </si>
+  <si>
+    <t>LAI1-CROPWAT-Tititcaca</t>
+  </si>
+  <si>
+    <t>LAI2-Sensor-Tiititcaca</t>
+  </si>
+  <si>
+    <t>LAI3-Farmer-Titicaca</t>
+  </si>
+  <si>
+    <t>LAI4-CROPWAT-ICBA</t>
+  </si>
+  <si>
+    <t>LAI6-Farmer-ICBA</t>
+  </si>
+  <si>
+    <t>LAI5-Sensor-ICBA</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +114,12 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -116,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -129,6 +154,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -151,7 +185,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -610,7 +644,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2239,245 +2273,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet3 (2)"/>
-      <sheetName val="LAI Raw data"/>
-      <sheetName val="LAI cleaned"/>
-      <sheetName val="Sheet5"/>
-      <sheetName val="Sheet3"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>LAI 1-CROPWAT Tititcaca</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>LAI 2 -Sensor Tiititcaca</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>LAI 3  - Farmer Titicaca</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2">
-            <v>0.65</v>
-          </cell>
-          <cell r="F2">
-            <v>0.12</v>
-          </cell>
-          <cell r="I2">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>0.65</v>
-          </cell>
-          <cell r="F3">
-            <v>0.5</v>
-          </cell>
-          <cell r="I3">
-            <v>0.56000000000000005</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>1.25</v>
-          </cell>
-          <cell r="F4">
-            <v>1.1599999999999999</v>
-          </cell>
-          <cell r="I4">
-            <v>1.07</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>1.32</v>
-          </cell>
-          <cell r="I5">
-            <v>1.5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>1.79</v>
-          </cell>
-          <cell r="I6">
-            <v>2.48</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>2.2599999999999998</v>
-          </cell>
-          <cell r="F7">
-            <v>2.21</v>
-          </cell>
-          <cell r="I7">
-            <v>2.63</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>1.88</v>
-          </cell>
-          <cell r="F8">
-            <v>2.89</v>
-          </cell>
-          <cell r="I8">
-            <v>2.68</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>1.91</v>
-          </cell>
-          <cell r="F9">
-            <v>2.6</v>
-          </cell>
-          <cell r="I9">
-            <v>2.35</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>1.78</v>
-          </cell>
-          <cell r="F10">
-            <v>2.38</v>
-          </cell>
-          <cell r="I10">
-            <v>2.44</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>LAI 4  - CROPWAT ICBA</v>
-          </cell>
-          <cell r="F20" t="str">
-            <v>LAI   5 Sensor ICBA</v>
-          </cell>
-          <cell r="I20" t="str">
-            <v>LAI   6 Farmer ICBA</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>0.74</v>
-          </cell>
-          <cell r="F21">
-            <v>0.37</v>
-          </cell>
-          <cell r="I21">
-            <v>0.21</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>0.6</v>
-          </cell>
-          <cell r="F22">
-            <v>0.52</v>
-          </cell>
-          <cell r="I22">
-            <v>0.64</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>1.1200000000000001</v>
-          </cell>
-          <cell r="F23">
-            <v>1.01</v>
-          </cell>
-          <cell r="I23">
-            <v>1.17</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>1.66</v>
-          </cell>
-          <cell r="F24">
-            <v>1.67</v>
-          </cell>
-          <cell r="I24">
-            <v>1.68</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25">
-            <v>2.29</v>
-          </cell>
-          <cell r="F25">
-            <v>2.37</v>
-          </cell>
-          <cell r="I25">
-            <v>2.44</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>2.61</v>
-          </cell>
-          <cell r="F26">
-            <v>2.84</v>
-          </cell>
-          <cell r="I26">
-            <v>2.72</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>2.7</v>
-          </cell>
-          <cell r="F27">
-            <v>2.44</v>
-          </cell>
-          <cell r="I27">
-            <v>2.61</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28">
-            <v>1.82</v>
-          </cell>
-          <cell r="F28">
-            <v>1.96</v>
-          </cell>
-          <cell r="I28">
-            <v>2.17</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>1.67</v>
-          </cell>
-          <cell r="F29">
-            <v>1.8</v>
-          </cell>
-          <cell r="I29">
-            <v>2.0099999999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2796,19 +2591,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD565DD-D9A8-4BE7-9C3E-B1E80C5B38E0}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" customWidth="1"/>
-    <col min="2" max="2" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" customWidth="1"/>
-    <col min="6" max="6" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.90625" customWidth="1"/>
-    <col min="8" max="8" width="17.7265625" customWidth="1"/>
-    <col min="9" max="9" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2832,7 +2627,7 @@
       </c>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>20250207</v>
       </c>
@@ -2855,7 +2650,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>20250213</v>
       </c>
@@ -2878,7 +2673,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>20250220</v>
       </c>
@@ -2901,7 +2696,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2920,7 +2715,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2939,7 +2734,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>20250313</v>
       </c>
@@ -2962,7 +2757,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>20250320</v>
       </c>
@@ -2985,7 +2780,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>20250327</v>
       </c>
@@ -3008,7 +2803,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>20250403</v>
       </c>
@@ -3031,7 +2826,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -3042,7 +2837,7 @@
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -3053,7 +2848,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -3064,7 +2859,7 @@
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3075,7 +2870,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -3086,7 +2881,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -3097,7 +2892,7 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -3108,7 +2903,7 @@
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -3119,7 +2914,7 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -3130,7 +2925,7 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3153,7 +2948,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>20250207</v>
       </c>
@@ -3176,7 +2971,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>20250213</v>
       </c>
@@ -3199,7 +2994,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>20250220</v>
       </c>
@@ -3222,7 +3017,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>20250227</v>
       </c>
@@ -3245,7 +3040,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>20250306</v>
       </c>
@@ -3268,7 +3063,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20250313</v>
       </c>
@@ -3291,7 +3086,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>20250320</v>
       </c>
@@ -3314,7 +3109,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>20250327</v>
       </c>
@@ -3337,7 +3132,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>20250403</v>
       </c>
@@ -3364,4 +3159,250 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DA6A21-36A5-2342-86E4-3D1CDD143A47}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>45695</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>45701</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>45708</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.07</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>45715</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4">
+        <v>1.32</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.66</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>45722</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4">
+        <v>1.79</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2.48</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2.29</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2.37</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>45729</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2.21</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2.63</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2.61</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2.84</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>45736</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.88</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2.89</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2.68</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>45743</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.91</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2.35</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.82</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>45750</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.78</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2.38</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2.44</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1.67</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="G10" s="5">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/data/LAI_data_S1.xlsx
+++ b/data/LAI_data_S1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beppe2hd/PycharmProjects/PureCircle/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E5892F-07E6-2549-AD93-F4C255211A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0547132-8B9F-AB49-9A2D-106B5A5C1F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12880" yWindow="6980" windowWidth="51900" windowHeight="24360" activeTab="1" xr2:uid="{7C517B69-0235-47A6-840A-4957514BDF8E}"/>
   </bookViews>
